--- a/summary_completeness_usco.xlsx
+++ b/summary_completeness_usco.xlsx
@@ -5,19 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/frzagaria/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/frzagaria/mypostdoc/usco_cosizes/tables_leon/tables_paper/github_completeness/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43BD8AE5-AA53-4F43-9622-E8B12D22D34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F073D642-B022-8941-81CF-4DDA66666E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30300" yWindow="5160" windowWidth="30200" windowHeight="17440" activeTab="1" xr2:uid="{D1CBB7E6-F27B-B349-915E-7B35683F7C0A}"/>
+    <workbookView xWindow="-1840" yWindow="10760" windowWidth="30200" windowHeight="17440" activeTab="2" xr2:uid="{D1CBB7E6-F27B-B349-915E-7B35683F7C0A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="38">
   <si>
     <t>Ks</t>
   </si>
@@ -173,6 +173,18 @@
   <si>
     <t>Cluster 13</t>
   </si>
+  <si>
+    <t>Lup 706 is a disc-bearing star in WISE</t>
+  </si>
+  <si>
+    <t>This does not include Lup 706</t>
+  </si>
+  <si>
+    <t>The five BD discs in Sanchis don't have CO fluxes. Only three are Lupus members!</t>
+  </si>
+  <si>
+    <t>Remove &lt;5sigma detections</t>
+  </si>
 </sst>
 </file>
 
@@ -240,7 +252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -256,6 +268,10 @@
     </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -570,7 +586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{645DD8AB-1B6C-5E44-9D66-BB02E54A4543}">
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
@@ -1279,7 +1295,7 @@
         <v>0.32972972972972975</v>
       </c>
       <c r="C20" s="6">
-        <f t="shared" ref="C20:K20" si="4">C18/C17</f>
+        <f t="shared" ref="C20:J20" si="4">C18/C17</f>
         <v>0.33888888888888891</v>
       </c>
       <c r="D20" s="6">
@@ -1334,7 +1350,7 @@
         <v>0.23243243243243245</v>
       </c>
       <c r="C21" s="6">
-        <f t="shared" ref="C21:K21" si="6">C19/C17</f>
+        <f t="shared" ref="C21:J21" si="6">C19/C17</f>
         <v>0.2388888888888889</v>
       </c>
       <c r="D21" s="6">
@@ -1378,6 +1394,150 @@
       <c r="O21" s="6">
         <f t="shared" si="7"/>
         <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+      <c r="A22" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="5">
+        <v>76</v>
+      </c>
+      <c r="E22" s="5">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+      <c r="A23" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="5">
+        <v>55</v>
+      </c>
+      <c r="E23" s="5">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+      <c r="D24" s="5">
+        <v>39</v>
+      </c>
+      <c r="E24" s="5">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+      <c r="D25" s="6">
+        <f>D23/D22</f>
+        <v>0.72368421052631582</v>
+      </c>
+      <c r="E25" s="6">
+        <f>E23/E22</f>
+        <v>0.75342465753424659</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+      <c r="D26" s="6">
+        <f>D24/D22</f>
+        <v>0.51315789473684215</v>
+      </c>
+      <c r="E26" s="6">
+        <f>E24/E22</f>
+        <v>0.53424657534246578</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="23" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="5">
+        <v>77</v>
+      </c>
+      <c r="E27" s="5">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+      <c r="D28" s="5">
+        <v>55</v>
+      </c>
+      <c r="E28" s="5">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+      <c r="D29" s="5">
+        <v>40</v>
+      </c>
+      <c r="E29" s="5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+      <c r="D30" s="6">
+        <f>D28/D27</f>
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="E30" s="6">
+        <f>E28/E27</f>
+        <v>0.7432432432432432</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+      <c r="D31" s="6">
+        <f>D29/D27</f>
+        <v>0.51948051948051943</v>
+      </c>
+      <c r="E31" s="6">
+        <f>E29/E27</f>
+        <v>0.54054054054054057</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+      <c r="D32" s="5">
+        <v>76</v>
+      </c>
+      <c r="E32" s="5">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="23" x14ac:dyDescent="0.2">
+      <c r="D33" s="5">
+        <v>55</v>
+      </c>
+      <c r="E33" s="5">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="24" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D34" s="5">
+        <v>28</v>
+      </c>
+      <c r="E34" s="5">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="23" x14ac:dyDescent="0.2">
+      <c r="D35" s="6">
+        <f t="shared" ref="D35:E35" si="8">D33/D32</f>
+        <v>0.72368421052631582</v>
+      </c>
+      <c r="E35" s="6">
+        <f t="shared" si="8"/>
+        <v>0.75342465753424659</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="23" x14ac:dyDescent="0.2">
+      <c r="D36" s="6">
+        <f t="shared" ref="D36:E36" si="9">D34/D32</f>
+        <v>0.36842105263157893</v>
+      </c>
+      <c r="E36" s="6">
+        <f t="shared" si="9"/>
+        <v>0.38356164383561642</v>
       </c>
     </row>
   </sheetData>
@@ -1387,18 +1547,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E403504B-BC7B-924E-A86C-511D0103391B}">
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="24" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>19</v>
       </c>
@@ -1415,7 +1575,7 @@
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
     </row>
-    <row r="3" spans="1:16" ht="24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="24" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>20</v>
       </c>
@@ -1453,7 +1613,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="24" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
@@ -1503,7 +1663,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" ht="24" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>10</v>
       </c>
@@ -1552,8 +1712,9 @@
       <c r="P5" s="1">
         <v>168</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" ht="24" x14ac:dyDescent="0.3">
+      <c r="Q5" s="9"/>
+    </row>
+    <row r="6" spans="1:17" ht="24" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
@@ -1603,7 +1764,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" ht="24" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
@@ -1653,7 +1814,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" ht="24" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
@@ -1703,7 +1864,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" ht="24" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
@@ -1768,7 +1929,7 @@
         <v>0.61904761904761907</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" ht="24" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>16</v>
       </c>
@@ -1840,19 +2001,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FBAADF2-5B59-D946-90FE-72E2266E87F2}">
-  <dimension ref="A1:AW10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AW91"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="24" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
-    <col min="2" max="41" width="13.83203125" customWidth="1"/>
+    <col min="2" max="10" width="13.83203125" customWidth="1"/>
+    <col min="11" max="11" width="13.83203125" style="1" customWidth="1"/>
+    <col min="12" max="41" width="13.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:49" ht="24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>26</v>
@@ -1867,7 +2030,6 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
       <c r="L2" s="1" t="s">
         <v>28</v>
       </c>
@@ -1919,7 +2081,7 @@
       <c r="AV2" s="1"/>
       <c r="AW2" s="1"/>
     </row>
-    <row r="3" spans="1:49" ht="24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
         <v>20</v>
@@ -1946,7 +2108,6 @@
       <c r="J3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="1"/>
       <c r="L3" s="1" t="s">
         <v>20</v>
       </c>
@@ -2034,7 +2195,7 @@
       <c r="AV3" s="1"/>
       <c r="AW3" s="1"/>
     </row>
-    <row r="4" spans="1:49" ht="24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
@@ -2065,7 +2226,6 @@
       <c r="J4" s="1">
         <v>142</v>
       </c>
-      <c r="K4" s="1"/>
       <c r="L4" s="1">
         <v>691</v>
       </c>
@@ -2159,7 +2319,7 @@
       <c r="AV4" s="1"/>
       <c r="AW4" s="1"/>
     </row>
-    <row r="5" spans="1:49" ht="24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>10</v>
       </c>
@@ -2190,7 +2350,6 @@
       <c r="J5" s="1">
         <v>138</v>
       </c>
-      <c r="K5" s="1"/>
       <c r="L5" s="1">
         <v>611</v>
       </c>
@@ -2284,7 +2443,7 @@
       <c r="AV5" s="1"/>
       <c r="AW5" s="1"/>
     </row>
-    <row r="6" spans="1:49" ht="24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
@@ -2315,7 +2474,6 @@
       <c r="J6" s="1">
         <v>41</v>
       </c>
-      <c r="K6" s="1"/>
       <c r="L6" s="1">
         <v>111</v>
       </c>
@@ -2409,7 +2567,7 @@
       <c r="AV6" s="1"/>
       <c r="AW6" s="1"/>
     </row>
-    <row r="7" spans="1:49" ht="24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
@@ -2440,7 +2598,6 @@
       <c r="J7" s="1">
         <v>25</v>
       </c>
-      <c r="K7" s="1"/>
       <c r="L7" s="1">
         <v>61</v>
       </c>
@@ -2520,10 +2677,10 @@
         <v>45</v>
       </c>
       <c r="AN7" s="1">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AO7" s="1">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AP7" s="1"/>
       <c r="AQ7" s="1"/>
@@ -2534,7 +2691,7 @@
       <c r="AV7" s="1"/>
       <c r="AW7" s="1"/>
     </row>
-    <row r="8" spans="1:49" ht="24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
@@ -2565,7 +2722,6 @@
       <c r="J8" s="1">
         <v>17</v>
       </c>
-      <c r="K8" s="1"/>
       <c r="L8" s="1">
         <v>30</v>
       </c>
@@ -2645,10 +2801,10 @@
         <v>33</v>
       </c>
       <c r="AN8" s="1">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AO8" s="1">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="1"/>
@@ -2659,7 +2815,7 @@
       <c r="AV8" s="1"/>
       <c r="AW8" s="1"/>
     </row>
-    <row r="9" spans="1:49" ht="24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
@@ -2668,23 +2824,23 @@
         <v>0.10975609756097561</v>
       </c>
       <c r="C9" s="7">
-        <f t="shared" ref="C9:K9" si="0">C7/C6</f>
+        <f>C7/C6</f>
         <v>8.7431693989071038E-2</v>
       </c>
       <c r="D9" s="7">
-        <f t="shared" si="0"/>
+        <f>D7/D6</f>
         <v>0.11428571428571428</v>
       </c>
       <c r="E9" s="7">
-        <f t="shared" si="0"/>
+        <f>E7/E6</f>
         <v>0.10714285714285714</v>
       </c>
       <c r="F9" s="7">
-        <f t="shared" si="0"/>
+        <f>F7/F6</f>
         <v>0.10975609756097561</v>
       </c>
       <c r="G9" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="C9:J9" si="0">G7/G6</f>
         <v>0.64102564102564108</v>
       </c>
       <c r="H9" s="7">
@@ -2805,11 +2961,11 @@
       </c>
       <c r="AN9" s="7">
         <f t="shared" si="1"/>
-        <v>0.59090909090909094</v>
+        <v>0.625</v>
       </c>
       <c r="AO9" s="7">
         <f t="shared" si="1"/>
-        <v>0.61904761904761907</v>
+        <v>0.65476190476190477</v>
       </c>
       <c r="AP9" s="1"/>
       <c r="AQ9" s="1"/>
@@ -2820,7 +2976,7 @@
       <c r="AV9" s="1"/>
       <c r="AW9" s="1"/>
     </row>
-    <row r="10" spans="1:49" ht="24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>16</v>
       </c>
@@ -2829,23 +2985,23 @@
         <v>3.6585365853658534E-2</v>
       </c>
       <c r="C10" s="7">
-        <f t="shared" ref="C10:K10" si="2">C8/C6</f>
+        <f>C8/C6</f>
         <v>3.2786885245901641E-2</v>
       </c>
       <c r="D10" s="7">
-        <f t="shared" si="2"/>
+        <f>D8/D6</f>
         <v>3.5714285714285712E-2</v>
       </c>
       <c r="E10" s="7">
-        <f t="shared" si="2"/>
+        <f>E8/E6</f>
         <v>4.1666666666666664E-2</v>
       </c>
       <c r="F10" s="7">
-        <f t="shared" si="2"/>
+        <f>F8/F6</f>
         <v>4.2682926829268296E-2</v>
       </c>
       <c r="G10" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="C10:J10" si="2">G8/G6</f>
         <v>0.46153846153846156</v>
       </c>
       <c r="H10" s="7">
@@ -2966,11 +3122,11 @@
       </c>
       <c r="AN10" s="7">
         <f t="shared" si="3"/>
-        <v>0.40909090909090912</v>
+        <v>0.44318181818181818</v>
       </c>
       <c r="AO10" s="7">
         <f t="shared" si="3"/>
-        <v>0.42857142857142855</v>
+        <v>0.4642857142857143</v>
       </c>
       <c r="AP10" s="1"/>
       <c r="AQ10" s="1"/>
@@ -2981,6 +3137,2072 @@
       <c r="AV10" s="1"/>
       <c r="AW10" s="1"/>
     </row>
+    <row r="12" spans="1:49" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:49" x14ac:dyDescent="0.3">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:49" x14ac:dyDescent="0.3">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:49" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1">
+        <v>535</v>
+      </c>
+      <c r="C15" s="1">
+        <v>535</v>
+      </c>
+      <c r="D15" s="1">
+        <v>535</v>
+      </c>
+      <c r="E15" s="1">
+        <v>439</v>
+      </c>
+      <c r="F15" s="1">
+        <v>439</v>
+      </c>
+      <c r="G15" s="1">
+        <v>51</v>
+      </c>
+      <c r="I15" s="1">
+        <v>128</v>
+      </c>
+      <c r="J15" s="1">
+        <v>128</v>
+      </c>
+      <c r="K15" s="1">
+        <v>199</v>
+      </c>
+      <c r="L15" s="1">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="16" spans="1:49" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="1">
+        <v>442</v>
+      </c>
+      <c r="C16" s="8">
+        <v>442</v>
+      </c>
+      <c r="D16" s="1">
+        <v>370</v>
+      </c>
+      <c r="E16" s="1">
+        <v>430</v>
+      </c>
+      <c r="F16" s="1">
+        <v>426</v>
+      </c>
+      <c r="G16" s="1">
+        <v>50</v>
+      </c>
+      <c r="I16" s="1">
+        <v>128</v>
+      </c>
+      <c r="J16" s="1">
+        <v>127</v>
+      </c>
+      <c r="K16" s="1">
+        <v>192</v>
+      </c>
+      <c r="L16" s="1">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="1">
+        <v>164</v>
+      </c>
+      <c r="C17" s="1">
+        <v>183</v>
+      </c>
+      <c r="D17" s="1">
+        <v>140</v>
+      </c>
+      <c r="E17" s="1">
+        <v>168</v>
+      </c>
+      <c r="F17" s="1">
+        <v>164</v>
+      </c>
+      <c r="G17" s="1">
+        <v>28</v>
+      </c>
+      <c r="I17" s="1">
+        <v>52</v>
+      </c>
+      <c r="J17" s="1">
+        <v>51</v>
+      </c>
+      <c r="K17" s="1">
+        <v>74</v>
+      </c>
+      <c r="L17" s="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="1">
+        <v>18</v>
+      </c>
+      <c r="C18" s="1">
+        <v>16</v>
+      </c>
+      <c r="D18" s="1">
+        <v>16</v>
+      </c>
+      <c r="E18" s="1">
+        <v>18</v>
+      </c>
+      <c r="F18" s="1">
+        <v>18</v>
+      </c>
+      <c r="G18" s="1">
+        <v>2</v>
+      </c>
+      <c r="I18" s="1">
+        <v>7</v>
+      </c>
+      <c r="J18" s="1">
+        <v>7</v>
+      </c>
+      <c r="K18" s="1">
+        <v>9</v>
+      </c>
+      <c r="L18" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="1">
+        <v>6</v>
+      </c>
+      <c r="C19" s="1">
+        <v>6</v>
+      </c>
+      <c r="D19" s="1">
+        <v>5</v>
+      </c>
+      <c r="E19" s="1">
+        <v>7</v>
+      </c>
+      <c r="F19" s="1">
+        <v>7</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1</v>
+      </c>
+      <c r="I19" s="1">
+        <v>4</v>
+      </c>
+      <c r="J19" s="1">
+        <v>4</v>
+      </c>
+      <c r="K19" s="1">
+        <v>2</v>
+      </c>
+      <c r="L19" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="7">
+        <f>B18/B17</f>
+        <v>0.10975609756097561</v>
+      </c>
+      <c r="C20" s="7">
+        <f>C18/C17</f>
+        <v>8.7431693989071038E-2</v>
+      </c>
+      <c r="D20" s="7">
+        <f>D18/D17</f>
+        <v>0.11428571428571428</v>
+      </c>
+      <c r="E20" s="7">
+        <f>E18/E17</f>
+        <v>0.10714285714285714</v>
+      </c>
+      <c r="F20" s="7">
+        <f>F18/F17</f>
+        <v>0.10975609756097561</v>
+      </c>
+      <c r="G20" s="7">
+        <f t="shared" ref="G20:L20" si="4">G18/G17</f>
+        <v>7.1428571428571425E-2</v>
+      </c>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7">
+        <f t="shared" si="4"/>
+        <v>0.13461538461538461</v>
+      </c>
+      <c r="J20" s="7">
+        <f t="shared" si="4"/>
+        <v>0.13725490196078433</v>
+      </c>
+      <c r="K20" s="7">
+        <f t="shared" si="4"/>
+        <v>0.12162162162162163</v>
+      </c>
+      <c r="L20" s="7">
+        <f t="shared" si="4"/>
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="7">
+        <f>B19/B17</f>
+        <v>3.6585365853658534E-2</v>
+      </c>
+      <c r="C21" s="7">
+        <f>C19/C17</f>
+        <v>3.2786885245901641E-2</v>
+      </c>
+      <c r="D21" s="7">
+        <f>D19/D17</f>
+        <v>3.5714285714285712E-2</v>
+      </c>
+      <c r="E21" s="7">
+        <f>E19/E17</f>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F21" s="7">
+        <f>F19/F17</f>
+        <v>4.2682926829268296E-2</v>
+      </c>
+      <c r="G21" s="7">
+        <f t="shared" ref="G21:L21" si="5">G19/G17</f>
+        <v>3.5714285714285712E-2</v>
+      </c>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7">
+        <f t="shared" si="5"/>
+        <v>7.6923076923076927E-2</v>
+      </c>
+      <c r="J21" s="7">
+        <f t="shared" si="5"/>
+        <v>7.8431372549019607E-2</v>
+      </c>
+      <c r="K21" s="7">
+        <f t="shared" si="5"/>
+        <v>2.7027027027027029E-2</v>
+      </c>
+      <c r="L21" s="7">
+        <f t="shared" si="5"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="1">
+        <v>160</v>
+      </c>
+      <c r="C25" s="1">
+        <v>160</v>
+      </c>
+      <c r="D25" s="1">
+        <v>160</v>
+      </c>
+      <c r="E25" s="1">
+        <v>142</v>
+      </c>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1">
+        <v>9</v>
+      </c>
+      <c r="I25" s="1">
+        <v>47</v>
+      </c>
+      <c r="K25" s="1">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B26" s="1">
+        <v>128</v>
+      </c>
+      <c r="C26" s="1">
+        <v>128</v>
+      </c>
+      <c r="D26" s="1">
+        <v>123</v>
+      </c>
+      <c r="E26" s="1">
+        <v>138</v>
+      </c>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1">
+        <v>9</v>
+      </c>
+      <c r="I26" s="1">
+        <v>45</v>
+      </c>
+      <c r="K26" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" s="1">
+        <v>39</v>
+      </c>
+      <c r="C27" s="1">
+        <v>40</v>
+      </c>
+      <c r="D27" s="1">
+        <v>39</v>
+      </c>
+      <c r="E27" s="1">
+        <v>41</v>
+      </c>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1">
+        <v>3</v>
+      </c>
+      <c r="I27" s="1">
+        <v>11</v>
+      </c>
+      <c r="K27" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="1">
+        <v>25</v>
+      </c>
+      <c r="C28" s="1">
+        <v>24</v>
+      </c>
+      <c r="D28" s="1">
+        <v>24</v>
+      </c>
+      <c r="E28" s="1">
+        <v>25</v>
+      </c>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1">
+        <v>3</v>
+      </c>
+      <c r="I28" s="1">
+        <v>8</v>
+      </c>
+      <c r="K28" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="1">
+        <v>18</v>
+      </c>
+      <c r="C29" s="1">
+        <v>17</v>
+      </c>
+      <c r="D29" s="1">
+        <v>17</v>
+      </c>
+      <c r="E29" s="1">
+        <v>17</v>
+      </c>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1">
+        <v>3</v>
+      </c>
+      <c r="I29" s="1">
+        <v>7</v>
+      </c>
+      <c r="K29" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" s="7">
+        <f t="shared" ref="B30:F30" si="6">B28/B27</f>
+        <v>0.64102564102564108</v>
+      </c>
+      <c r="C30" s="7">
+        <f t="shared" si="6"/>
+        <v>0.6</v>
+      </c>
+      <c r="D30" s="7">
+        <f t="shared" si="6"/>
+        <v>0.61538461538461542</v>
+      </c>
+      <c r="E30" s="7">
+        <f t="shared" si="6"/>
+        <v>0.6097560975609756</v>
+      </c>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7">
+        <f t="shared" ref="F30:K30" si="7">G28/G27</f>
+        <v>1</v>
+      </c>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7">
+        <f t="shared" si="7"/>
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7">
+        <f t="shared" si="7"/>
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" s="7">
+        <f t="shared" ref="B31:F31" si="8">B29/B27</f>
+        <v>0.46153846153846156</v>
+      </c>
+      <c r="C31" s="7">
+        <f t="shared" si="8"/>
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="D31" s="7">
+        <f t="shared" si="8"/>
+        <v>0.4358974358974359</v>
+      </c>
+      <c r="E31" s="7">
+        <f t="shared" si="8"/>
+        <v>0.41463414634146339</v>
+      </c>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7">
+        <f t="shared" ref="F31:K31" si="9">G29/G27</f>
+        <v>1</v>
+      </c>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7">
+        <f t="shared" si="9"/>
+        <v>0.63636363636363635</v>
+      </c>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7">
+        <f t="shared" si="9"/>
+        <v>0.29166666666666669</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="1">
+        <v>691</v>
+      </c>
+      <c r="C35" s="1">
+        <v>691</v>
+      </c>
+      <c r="D35" s="1">
+        <v>691</v>
+      </c>
+      <c r="E35" s="1">
+        <v>654</v>
+      </c>
+      <c r="F35" s="1">
+        <v>654</v>
+      </c>
+      <c r="G35" s="1">
+        <v>39</v>
+      </c>
+      <c r="I35" s="1">
+        <v>138</v>
+      </c>
+      <c r="J35" s="1">
+        <v>138</v>
+      </c>
+      <c r="K35" s="1">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36" s="1">
+        <v>611</v>
+      </c>
+      <c r="C36" s="1">
+        <v>611</v>
+      </c>
+      <c r="D36" s="1">
+        <v>584</v>
+      </c>
+      <c r="E36" s="1">
+        <v>645</v>
+      </c>
+      <c r="F36" s="1">
+        <v>642</v>
+      </c>
+      <c r="G36" s="1">
+        <v>36</v>
+      </c>
+      <c r="I36" s="1">
+        <v>137</v>
+      </c>
+      <c r="J36" s="1">
+        <v>136</v>
+      </c>
+      <c r="K36" s="1">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37" s="1">
+        <v>111</v>
+      </c>
+      <c r="C37" s="1">
+        <v>110</v>
+      </c>
+      <c r="D37" s="1">
+        <v>105</v>
+      </c>
+      <c r="E37" s="1">
+        <v>118</v>
+      </c>
+      <c r="F37" s="1">
+        <v>115</v>
+      </c>
+      <c r="G37" s="1">
+        <v>5</v>
+      </c>
+      <c r="I37" s="1">
+        <v>27</v>
+      </c>
+      <c r="J37" s="1">
+        <v>26</v>
+      </c>
+      <c r="K37" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" s="1">
+        <v>61</v>
+      </c>
+      <c r="C38" s="1">
+        <v>61</v>
+      </c>
+      <c r="D38" s="1">
+        <v>64</v>
+      </c>
+      <c r="E38" s="1">
+        <v>72</v>
+      </c>
+      <c r="F38" s="1">
+        <v>72</v>
+      </c>
+      <c r="G38" s="1">
+        <v>5</v>
+      </c>
+      <c r="I38" s="1">
+        <v>22</v>
+      </c>
+      <c r="J38" s="1">
+        <v>22</v>
+      </c>
+      <c r="K38" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39" s="1">
+        <v>30</v>
+      </c>
+      <c r="C39" s="1">
+        <v>30</v>
+      </c>
+      <c r="D39" s="1">
+        <v>29</v>
+      </c>
+      <c r="E39" s="1">
+        <v>32</v>
+      </c>
+      <c r="F39" s="1">
+        <v>32</v>
+      </c>
+      <c r="G39" s="1">
+        <v>4</v>
+      </c>
+      <c r="I39" s="1">
+        <v>16</v>
+      </c>
+      <c r="J39" s="1">
+        <v>16</v>
+      </c>
+      <c r="K39" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" s="7">
+        <f t="shared" ref="B40:F40" si="10">B38/B37</f>
+        <v>0.5495495495495496</v>
+      </c>
+      <c r="C40" s="7">
+        <f t="shared" si="10"/>
+        <v>0.55454545454545456</v>
+      </c>
+      <c r="D40" s="7">
+        <f t="shared" si="10"/>
+        <v>0.60952380952380958</v>
+      </c>
+      <c r="E40" s="7">
+        <f t="shared" si="10"/>
+        <v>0.61016949152542377</v>
+      </c>
+      <c r="F40" s="7">
+        <f t="shared" si="10"/>
+        <v>0.62608695652173918</v>
+      </c>
+      <c r="G40" s="7">
+        <f t="shared" ref="G40:K40" si="11">G38/G37</f>
+        <v>1</v>
+      </c>
+      <c r="H40" s="7"/>
+      <c r="I40" s="7">
+        <f t="shared" si="11"/>
+        <v>0.81481481481481477</v>
+      </c>
+      <c r="J40" s="7">
+        <f t="shared" si="11"/>
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="K40" s="7">
+        <f t="shared" si="11"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B41" s="7">
+        <f t="shared" ref="B41:F41" si="12">B39/B37</f>
+        <v>0.27027027027027029</v>
+      </c>
+      <c r="C41" s="7">
+        <f t="shared" si="12"/>
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="D41" s="7">
+        <f t="shared" si="12"/>
+        <v>0.27619047619047621</v>
+      </c>
+      <c r="E41" s="7">
+        <f t="shared" si="12"/>
+        <v>0.2711864406779661</v>
+      </c>
+      <c r="F41" s="7">
+        <f t="shared" si="12"/>
+        <v>0.27826086956521739</v>
+      </c>
+      <c r="G41" s="7">
+        <f t="shared" ref="G41:K41" si="13">G39/G37</f>
+        <v>0.8</v>
+      </c>
+      <c r="H41" s="7"/>
+      <c r="I41" s="7">
+        <f t="shared" si="13"/>
+        <v>0.59259259259259256</v>
+      </c>
+      <c r="J41" s="7">
+        <f t="shared" si="13"/>
+        <v>0.61538461538461542</v>
+      </c>
+      <c r="K41" s="7">
+        <f t="shared" si="13"/>
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A45" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" s="1">
+        <v>285</v>
+      </c>
+      <c r="C45" s="1">
+        <v>285</v>
+      </c>
+      <c r="D45" s="1">
+        <v>285</v>
+      </c>
+      <c r="E45" s="1">
+        <v>249</v>
+      </c>
+      <c r="G45" s="1">
+        <v>23</v>
+      </c>
+      <c r="I45" s="1">
+        <v>51</v>
+      </c>
+      <c r="K45" s="1">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A46" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B46" s="1">
+        <v>244</v>
+      </c>
+      <c r="C46" s="1">
+        <v>244</v>
+      </c>
+      <c r="D46" s="1">
+        <v>213</v>
+      </c>
+      <c r="E46" s="1">
+        <v>238</v>
+      </c>
+      <c r="G46" s="1">
+        <v>23</v>
+      </c>
+      <c r="I46" s="1">
+        <v>51</v>
+      </c>
+      <c r="K46" s="1">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" s="1">
+        <v>51</v>
+      </c>
+      <c r="C47" s="1">
+        <v>51</v>
+      </c>
+      <c r="D47" s="1">
+        <v>46</v>
+      </c>
+      <c r="E47" s="1">
+        <v>52</v>
+      </c>
+      <c r="G47" s="1">
+        <v>4</v>
+      </c>
+      <c r="I47" s="1">
+        <v>9</v>
+      </c>
+      <c r="K47" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" s="1">
+        <v>24</v>
+      </c>
+      <c r="C48" s="1">
+        <v>22</v>
+      </c>
+      <c r="D48" s="1">
+        <v>24</v>
+      </c>
+      <c r="E48" s="1">
+        <v>29</v>
+      </c>
+      <c r="G48" s="1">
+        <v>3</v>
+      </c>
+      <c r="I48" s="1">
+        <v>9</v>
+      </c>
+      <c r="K48" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B49" s="1">
+        <v>9</v>
+      </c>
+      <c r="C49" s="1">
+        <v>8</v>
+      </c>
+      <c r="D49" s="1">
+        <v>10</v>
+      </c>
+      <c r="E49" s="1">
+        <v>11</v>
+      </c>
+      <c r="G49" s="1">
+        <v>3</v>
+      </c>
+      <c r="I49" s="1">
+        <v>4</v>
+      </c>
+      <c r="K49" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" s="7">
+        <f t="shared" ref="B50:E50" si="14">B48/B47</f>
+        <v>0.47058823529411764</v>
+      </c>
+      <c r="C50" s="7">
+        <f t="shared" si="14"/>
+        <v>0.43137254901960786</v>
+      </c>
+      <c r="D50" s="7">
+        <f t="shared" si="14"/>
+        <v>0.52173913043478259</v>
+      </c>
+      <c r="E50" s="7">
+        <f t="shared" si="14"/>
+        <v>0.55769230769230771</v>
+      </c>
+      <c r="F50" s="7"/>
+      <c r="G50" s="7">
+        <f t="shared" ref="F50:K50" si="15">G48/G47</f>
+        <v>0.75</v>
+      </c>
+      <c r="H50" s="7"/>
+      <c r="I50" s="7">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="J50" s="7"/>
+      <c r="K50" s="7">
+        <f t="shared" si="15"/>
+        <v>0.45945945945945948</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A51" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B51" s="7">
+        <f t="shared" ref="B51:E51" si="16">B49/B47</f>
+        <v>0.17647058823529413</v>
+      </c>
+      <c r="C51" s="7">
+        <f t="shared" si="16"/>
+        <v>0.15686274509803921</v>
+      </c>
+      <c r="D51" s="7">
+        <f t="shared" si="16"/>
+        <v>0.21739130434782608</v>
+      </c>
+      <c r="E51" s="7">
+        <f t="shared" si="16"/>
+        <v>0.21153846153846154</v>
+      </c>
+      <c r="F51" s="7"/>
+      <c r="G51" s="7">
+        <f t="shared" ref="F51:K51" si="17">G49/G47</f>
+        <v>0.75</v>
+      </c>
+      <c r="H51" s="7"/>
+      <c r="I51" s="7">
+        <f t="shared" si="17"/>
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="J51" s="7"/>
+      <c r="K51" s="7">
+        <f t="shared" si="17"/>
+        <v>0.10810810810810811</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A53" s="1"/>
+      <c r="B53" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="1"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A54" s="1"/>
+      <c r="B54" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A55" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B55" s="8">
+        <v>544</v>
+      </c>
+      <c r="C55" s="8">
+        <v>544</v>
+      </c>
+      <c r="D55" s="8">
+        <v>544</v>
+      </c>
+      <c r="E55" s="8">
+        <v>453</v>
+      </c>
+      <c r="F55" s="8">
+        <v>453</v>
+      </c>
+      <c r="G55" s="8">
+        <v>28</v>
+      </c>
+      <c r="I55" s="8">
+        <v>101</v>
+      </c>
+      <c r="K55" s="8">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A56" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B56" s="8">
+        <v>467</v>
+      </c>
+      <c r="C56" s="8">
+        <v>467</v>
+      </c>
+      <c r="D56" s="8">
+        <v>398</v>
+      </c>
+      <c r="E56" s="8">
+        <v>446</v>
+      </c>
+      <c r="F56" s="1">
+        <v>445</v>
+      </c>
+      <c r="G56" s="8">
+        <v>28</v>
+      </c>
+      <c r="I56" s="8">
+        <v>101</v>
+      </c>
+      <c r="K56" s="1">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A57" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B57" s="1">
+        <v>58</v>
+      </c>
+      <c r="C57" s="1">
+        <v>60</v>
+      </c>
+      <c r="D57" s="1">
+        <v>40</v>
+      </c>
+      <c r="E57" s="1">
+        <v>47</v>
+      </c>
+      <c r="F57" s="1">
+        <v>46</v>
+      </c>
+      <c r="G57" s="1">
+        <v>2</v>
+      </c>
+      <c r="I57" s="1">
+        <v>6</v>
+      </c>
+      <c r="K57" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A58" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B58" s="8">
+        <v>17</v>
+      </c>
+      <c r="C58" s="8">
+        <v>15</v>
+      </c>
+      <c r="D58" s="8">
+        <v>16</v>
+      </c>
+      <c r="E58" s="8">
+        <v>18</v>
+      </c>
+      <c r="F58" s="1">
+        <v>18</v>
+      </c>
+      <c r="G58" s="8">
+        <v>2</v>
+      </c>
+      <c r="I58" s="8">
+        <v>5</v>
+      </c>
+      <c r="K58" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A59" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B59" s="8">
+        <v>6</v>
+      </c>
+      <c r="C59" s="8">
+        <v>6</v>
+      </c>
+      <c r="D59" s="8">
+        <v>4</v>
+      </c>
+      <c r="E59" s="8">
+        <v>4</v>
+      </c>
+      <c r="F59" s="1">
+        <v>4</v>
+      </c>
+      <c r="G59" s="8">
+        <v>2</v>
+      </c>
+      <c r="I59" s="8">
+        <v>1</v>
+      </c>
+      <c r="K59" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A60" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" s="7">
+        <f t="shared" ref="B60:F60" si="18">B58/B57</f>
+        <v>0.29310344827586204</v>
+      </c>
+      <c r="C60" s="7">
+        <f t="shared" si="18"/>
+        <v>0.25</v>
+      </c>
+      <c r="D60" s="7">
+        <f t="shared" si="18"/>
+        <v>0.4</v>
+      </c>
+      <c r="E60" s="7">
+        <f t="shared" si="18"/>
+        <v>0.38297872340425532</v>
+      </c>
+      <c r="F60" s="7">
+        <f t="shared" si="18"/>
+        <v>0.39130434782608697</v>
+      </c>
+      <c r="G60" s="7">
+        <f t="shared" ref="G60:K60" si="19">G58/G57</f>
+        <v>1</v>
+      </c>
+      <c r="H60" s="7"/>
+      <c r="I60" s="7">
+        <f t="shared" si="19"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J60" s="7"/>
+      <c r="K60" s="7">
+        <f t="shared" si="19"/>
+        <v>0.34375</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A61" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B61" s="7">
+        <f t="shared" ref="B61:F61" si="20">B59/B57</f>
+        <v>0.10344827586206896</v>
+      </c>
+      <c r="C61" s="7">
+        <f t="shared" si="20"/>
+        <v>0.1</v>
+      </c>
+      <c r="D61" s="7">
+        <f t="shared" si="20"/>
+        <v>0.1</v>
+      </c>
+      <c r="E61" s="7">
+        <f t="shared" si="20"/>
+        <v>8.5106382978723402E-2</v>
+      </c>
+      <c r="F61" s="7">
+        <f t="shared" si="20"/>
+        <v>8.6956521739130432E-2</v>
+      </c>
+      <c r="G61" s="7">
+        <f t="shared" ref="G61:K61" si="21">G59/G57</f>
+        <v>1</v>
+      </c>
+      <c r="H61" s="7"/>
+      <c r="I61" s="7">
+        <f t="shared" si="21"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="J61" s="7"/>
+      <c r="K61" s="7">
+        <f t="shared" si="21"/>
+        <v>3.125E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A63" s="1"/>
+      <c r="B63" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="8"/>
+      <c r="D63" s="8"/>
+      <c r="E63" s="8"/>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A64" s="1"/>
+      <c r="B64" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A65" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B65" s="8">
+        <v>502</v>
+      </c>
+      <c r="C65" s="8">
+        <v>502</v>
+      </c>
+      <c r="D65" s="8">
+        <v>502</v>
+      </c>
+      <c r="E65" s="8">
+        <v>361</v>
+      </c>
+      <c r="G65" s="8">
+        <v>18</v>
+      </c>
+      <c r="I65" s="8">
+        <v>72</v>
+      </c>
+      <c r="K65" s="1">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A66" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B66" s="8">
+        <v>428</v>
+      </c>
+      <c r="C66" s="8">
+        <v>428</v>
+      </c>
+      <c r="D66" s="8">
+        <v>318</v>
+      </c>
+      <c r="E66" s="8">
+        <v>354</v>
+      </c>
+      <c r="G66" s="8">
+        <v>18</v>
+      </c>
+      <c r="I66" s="8">
+        <v>71</v>
+      </c>
+      <c r="K66" s="1">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A67" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B67" s="1">
+        <v>61</v>
+      </c>
+      <c r="C67" s="1">
+        <v>57</v>
+      </c>
+      <c r="D67" s="1">
+        <v>38</v>
+      </c>
+      <c r="E67" s="1">
+        <v>45</v>
+      </c>
+      <c r="G67" s="1">
+        <v>5</v>
+      </c>
+      <c r="I67" s="1">
+        <v>7</v>
+      </c>
+      <c r="K67" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A68" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B68" s="8">
+        <v>20</v>
+      </c>
+      <c r="C68" s="8">
+        <v>16</v>
+      </c>
+      <c r="D68" s="8">
+        <v>16</v>
+      </c>
+      <c r="E68" s="8">
+        <v>16</v>
+      </c>
+      <c r="G68" s="8">
+        <v>1</v>
+      </c>
+      <c r="I68" s="8">
+        <v>4</v>
+      </c>
+      <c r="K68" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A69" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B69" s="8">
+        <v>7</v>
+      </c>
+      <c r="C69" s="8">
+        <v>6</v>
+      </c>
+      <c r="D69" s="8">
+        <v>3</v>
+      </c>
+      <c r="E69" s="8">
+        <v>3</v>
+      </c>
+      <c r="G69" s="8">
+        <v>1</v>
+      </c>
+      <c r="I69" s="8">
+        <v>1</v>
+      </c>
+      <c r="K69" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A70" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" s="7">
+        <f t="shared" ref="B70:E70" si="22">B68/B67</f>
+        <v>0.32786885245901637</v>
+      </c>
+      <c r="C70" s="7">
+        <f t="shared" si="22"/>
+        <v>0.2807017543859649</v>
+      </c>
+      <c r="D70" s="7">
+        <f t="shared" si="22"/>
+        <v>0.42105263157894735</v>
+      </c>
+      <c r="E70" s="7">
+        <f t="shared" si="22"/>
+        <v>0.35555555555555557</v>
+      </c>
+      <c r="F70" s="7"/>
+      <c r="G70" s="7">
+        <f t="shared" ref="F70:K70" si="23">G68/G67</f>
+        <v>0.2</v>
+      </c>
+      <c r="H70" s="7"/>
+      <c r="I70" s="7">
+        <f t="shared" si="23"/>
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="J70" s="7"/>
+      <c r="K70" s="7">
+        <f t="shared" si="23"/>
+        <v>0.43478260869565216</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A71" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B71" s="7">
+        <f t="shared" ref="B71:E71" si="24">B69/B67</f>
+        <v>0.11475409836065574</v>
+      </c>
+      <c r="C71" s="7">
+        <f t="shared" si="24"/>
+        <v>0.10526315789473684</v>
+      </c>
+      <c r="D71" s="7">
+        <f t="shared" si="24"/>
+        <v>7.8947368421052627E-2</v>
+      </c>
+      <c r="E71" s="7">
+        <f t="shared" si="24"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="F71" s="7"/>
+      <c r="G71" s="7">
+        <f t="shared" ref="F71:K71" si="25">G69/G67</f>
+        <v>0.2</v>
+      </c>
+      <c r="H71" s="7"/>
+      <c r="I71" s="7">
+        <f t="shared" si="25"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="J71" s="7"/>
+      <c r="K71" s="7">
+        <f t="shared" si="25"/>
+        <v>4.3478260869565216E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A73" s="1"/>
+      <c r="B73" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C73" s="8"/>
+      <c r="D73" s="8"/>
+      <c r="E73" s="8"/>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A74" s="1"/>
+      <c r="B74" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A75" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B75" s="8">
+        <v>240</v>
+      </c>
+      <c r="C75" s="8">
+        <v>240</v>
+      </c>
+      <c r="D75" s="8">
+        <v>240</v>
+      </c>
+      <c r="E75" s="8">
+        <v>225</v>
+      </c>
+      <c r="G75" s="8">
+        <v>11</v>
+      </c>
+      <c r="I75" s="8">
+        <v>28</v>
+      </c>
+      <c r="K75" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A76" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B76" s="8">
+        <v>302</v>
+      </c>
+      <c r="C76" s="8">
+        <v>302</v>
+      </c>
+      <c r="D76" s="8">
+        <v>189</v>
+      </c>
+      <c r="E76" s="8">
+        <v>219</v>
+      </c>
+      <c r="G76" s="8">
+        <v>11</v>
+      </c>
+      <c r="I76" s="8">
+        <v>27</v>
+      </c>
+      <c r="K76" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A77" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B77" s="1">
+        <v>17</v>
+      </c>
+      <c r="C77" s="1">
+        <v>21</v>
+      </c>
+      <c r="D77" s="1">
+        <v>18</v>
+      </c>
+      <c r="E77" s="1">
+        <v>20</v>
+      </c>
+      <c r="G77" s="1">
+        <v>0</v>
+      </c>
+      <c r="I77" s="1">
+        <v>2</v>
+      </c>
+      <c r="K77" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A78" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B78" s="8">
+        <v>7</v>
+      </c>
+      <c r="C78" s="8">
+        <v>7</v>
+      </c>
+      <c r="D78" s="8">
+        <v>7</v>
+      </c>
+      <c r="E78" s="8">
+        <v>7</v>
+      </c>
+      <c r="G78" s="8">
+        <v>0</v>
+      </c>
+      <c r="I78" s="8">
+        <v>1</v>
+      </c>
+      <c r="K78" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A79" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B79" s="8">
+        <v>1</v>
+      </c>
+      <c r="C79" s="8">
+        <v>1</v>
+      </c>
+      <c r="D79" s="8">
+        <v>1</v>
+      </c>
+      <c r="E79" s="8">
+        <v>1</v>
+      </c>
+      <c r="G79" s="8">
+        <v>0</v>
+      </c>
+      <c r="I79" s="8">
+        <v>1</v>
+      </c>
+      <c r="K79" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A80" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" s="7">
+        <f t="shared" ref="B80:E80" si="26">B78/B77</f>
+        <v>0.41176470588235292</v>
+      </c>
+      <c r="C80" s="7">
+        <f t="shared" si="26"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D80" s="7">
+        <f t="shared" si="26"/>
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="E80" s="7">
+        <f t="shared" si="26"/>
+        <v>0.35</v>
+      </c>
+      <c r="F80" s="7"/>
+      <c r="G80" s="7"/>
+      <c r="H80" s="7"/>
+      <c r="I80" s="7">
+        <f t="shared" ref="F80:K80" si="27">I78/I77</f>
+        <v>0.5</v>
+      </c>
+      <c r="J80" s="7"/>
+      <c r="K80" s="7">
+        <f t="shared" si="27"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A81" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B81" s="7">
+        <f t="shared" ref="B81:E81" si="28">B79/B77</f>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="C81" s="7">
+        <f t="shared" si="28"/>
+        <v>4.7619047619047616E-2</v>
+      </c>
+      <c r="D81" s="7">
+        <f t="shared" si="28"/>
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="E81" s="7">
+        <f t="shared" si="28"/>
+        <v>0.05</v>
+      </c>
+      <c r="F81" s="7"/>
+      <c r="G81" s="7"/>
+      <c r="H81" s="7"/>
+      <c r="I81" s="7">
+        <f t="shared" ref="F81:K81" si="29">I79/I77</f>
+        <v>0.5</v>
+      </c>
+      <c r="J81" s="7"/>
+      <c r="K81" s="7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A83" s="1"/>
+      <c r="B83" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C83" s="8"/>
+      <c r="D83" s="8"/>
+      <c r="E83" s="8"/>
+      <c r="F83" s="1"/>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A84" s="1"/>
+      <c r="B84" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A85" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B85" s="8">
+        <v>226</v>
+      </c>
+      <c r="C85" s="8">
+        <v>226</v>
+      </c>
+      <c r="D85" s="8">
+        <v>226</v>
+      </c>
+      <c r="E85" s="8">
+        <v>177</v>
+      </c>
+      <c r="F85" s="1">
+        <v>177</v>
+      </c>
+      <c r="G85" s="8">
+        <v>21</v>
+      </c>
+      <c r="I85" s="8">
+        <v>28</v>
+      </c>
+      <c r="K85" s="1">
+        <v>70</v>
+      </c>
+      <c r="L85" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A86" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B86" s="1">
+        <v>192</v>
+      </c>
+      <c r="C86" s="8">
+        <v>191</v>
+      </c>
+      <c r="D86" s="8">
+        <v>151</v>
+      </c>
+      <c r="E86" s="8">
+        <v>172</v>
+      </c>
+      <c r="F86" s="1">
+        <v>168</v>
+      </c>
+      <c r="G86" s="8">
+        <v>21</v>
+      </c>
+      <c r="I86" s="8">
+        <v>28</v>
+      </c>
+      <c r="K86" s="1">
+        <v>68</v>
+      </c>
+      <c r="L86" s="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A87" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B87" s="1">
+        <v>84</v>
+      </c>
+      <c r="C87" s="1">
+        <v>77</v>
+      </c>
+      <c r="D87" s="1">
+        <v>70</v>
+      </c>
+      <c r="E87" s="1">
+        <v>88</v>
+      </c>
+      <c r="F87" s="1">
+        <v>84</v>
+      </c>
+      <c r="G87" s="1">
+        <v>14</v>
+      </c>
+      <c r="I87" s="1">
+        <v>21</v>
+      </c>
+      <c r="K87" s="1">
+        <v>35</v>
+      </c>
+      <c r="L87" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A88" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B88" s="8">
+        <v>50</v>
+      </c>
+      <c r="C88" s="8">
+        <v>45</v>
+      </c>
+      <c r="D88" s="8">
+        <v>45</v>
+      </c>
+      <c r="E88" s="1">
+        <v>55</v>
+      </c>
+      <c r="F88" s="1">
+        <v>55</v>
+      </c>
+      <c r="G88" s="8">
+        <v>11</v>
+      </c>
+      <c r="I88" s="1">
+        <v>15</v>
+      </c>
+      <c r="K88" s="1">
+        <v>27</v>
+      </c>
+      <c r="L88" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A89" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B89" s="8">
+        <v>38</v>
+      </c>
+      <c r="C89" s="8">
+        <v>34</v>
+      </c>
+      <c r="D89" s="8">
+        <v>33</v>
+      </c>
+      <c r="E89" s="1">
+        <v>39</v>
+      </c>
+      <c r="F89" s="1">
+        <v>39</v>
+      </c>
+      <c r="G89" s="8">
+        <v>10</v>
+      </c>
+      <c r="I89" s="1">
+        <v>11</v>
+      </c>
+      <c r="K89" s="1">
+        <v>17</v>
+      </c>
+      <c r="L89" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A90" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" s="7">
+        <f t="shared" ref="B90:F90" si="30">B88/B87</f>
+        <v>0.59523809523809523</v>
+      </c>
+      <c r="C90" s="7">
+        <f t="shared" si="30"/>
+        <v>0.58441558441558439</v>
+      </c>
+      <c r="D90" s="7">
+        <f t="shared" si="30"/>
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="E90" s="7">
+        <f t="shared" si="30"/>
+        <v>0.625</v>
+      </c>
+      <c r="F90" s="7">
+        <f t="shared" si="30"/>
+        <v>0.65476190476190477</v>
+      </c>
+      <c r="G90" s="7">
+        <f t="shared" ref="G90:L90" si="31">G88/G87</f>
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="H90" s="7"/>
+      <c r="I90" s="7">
+        <f t="shared" si="31"/>
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="J90" s="7"/>
+      <c r="K90" s="7">
+        <f t="shared" si="31"/>
+        <v>0.77142857142857146</v>
+      </c>
+      <c r="L90" s="7">
+        <f t="shared" si="31"/>
+        <v>0.81818181818181823</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A91" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B91" s="7">
+        <f t="shared" ref="B91:F91" si="32">B89/B87</f>
+        <v>0.45238095238095238</v>
+      </c>
+      <c r="C91" s="7">
+        <f t="shared" si="32"/>
+        <v>0.44155844155844154</v>
+      </c>
+      <c r="D91" s="7">
+        <f t="shared" si="32"/>
+        <v>0.47142857142857142</v>
+      </c>
+      <c r="E91" s="7">
+        <f t="shared" si="32"/>
+        <v>0.44318181818181818</v>
+      </c>
+      <c r="F91" s="7">
+        <f t="shared" si="32"/>
+        <v>0.4642857142857143</v>
+      </c>
+      <c r="G91" s="7">
+        <f t="shared" ref="G91:L91" si="33">G89/G87</f>
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="H91" s="7"/>
+      <c r="I91" s="7">
+        <f t="shared" si="33"/>
+        <v>0.52380952380952384</v>
+      </c>
+      <c r="J91" s="7"/>
+      <c r="K91" s="7">
+        <f t="shared" si="33"/>
+        <v>0.48571428571428571</v>
+      </c>
+      <c r="L91" s="7">
+        <f t="shared" si="33"/>
+        <v>0.51515151515151514</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/summary_completeness_usco.xlsx
+++ b/summary_completeness_usco.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/frzagaria/mypostdoc/usco_cosizes/tables_leon/tables_paper/github_completeness/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F073D642-B022-8941-81CF-4DDA66666E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08358D6F-D60B-DF49-A7F3-B75930E6C5D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1840" yWindow="10760" windowWidth="30200" windowHeight="17440" activeTab="2" xr2:uid="{D1CBB7E6-F27B-B349-915E-7B35683F7C0A}"/>
+    <workbookView xWindow="51720" yWindow="5920" windowWidth="30200" windowHeight="17440" xr2:uid="{D1CBB7E6-F27B-B349-915E-7B35683F7C0A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="39">
   <si>
     <t>Ks</t>
   </si>
@@ -185,12 +185,15 @@
   <si>
     <t>Remove &lt;5sigma detections</t>
   </si>
+  <si>
+    <t>UpperSco Polnitzky (SpTs)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -231,6 +234,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri (Body)"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -252,7 +261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -272,6 +281,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -587,18 +597,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{645DD8AB-1B6C-5E44-9D66-BB02E54A4543}">
   <dimension ref="A1:O36"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="24" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.83203125" customWidth="1"/>
-    <col min="2" max="15" width="13.83203125" customWidth="1"/>
+    <col min="1" max="1" width="32.83203125" style="1" customWidth="1"/>
+    <col min="2" max="15" width="13.83203125" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -620,7 +631,7 @@
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
     </row>
-    <row r="3" spans="1:15" ht="23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="3" t="s">
         <v>1</v>
@@ -665,7 +676,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
@@ -709,7 +720,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>10</v>
       </c>
@@ -753,7 +764,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
@@ -797,7 +808,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
@@ -841,7 +852,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
@@ -885,7 +896,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
@@ -942,7 +953,7 @@
         <v>0.54374999999999996</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>16</v>
       </c>
@@ -999,12 +1010,12 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="21" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="23" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1026,7 +1037,7 @@
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
     </row>
-    <row r="14" spans="1:15" ht="23" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" s="3" t="s">
         <v>1</v>
@@ -1071,7 +1082,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>9</v>
       </c>
@@ -1114,7 +1125,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>10</v>
       </c>
@@ -1157,7 +1168,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>6</v>
       </c>
@@ -1200,7 +1211,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>7</v>
       </c>
@@ -1243,7 +1254,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>8</v>
       </c>
@@ -1286,7 +1297,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>15</v>
       </c>
@@ -1341,7 +1352,7 @@
         <v>0.80555555555555558</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>16</v>
       </c>
@@ -1396,7 +1407,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
         <v>35</v>
       </c>
@@ -1407,7 +1418,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>36</v>
       </c>
@@ -1418,7 +1429,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="D24" s="5">
         <v>39</v>
       </c>
@@ -1426,7 +1437,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="D25" s="6">
         <f>D23/D22</f>
         <v>0.72368421052631582</v>
@@ -1436,7 +1447,7 @@
         <v>0.75342465753424659</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="D26" s="6">
         <f>D24/D22</f>
         <v>0.51315789473684215</v>
@@ -1446,7 +1457,7 @@
         <v>0.53424657534246578</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="23" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>34</v>
       </c>
@@ -1457,7 +1468,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="D28" s="5">
         <v>55</v>
       </c>
@@ -1465,7 +1476,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="D29" s="5">
         <v>40</v>
       </c>
@@ -1473,7 +1484,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="D30" s="6">
         <f>D28/D27</f>
         <v>0.7142857142857143</v>
@@ -1483,7 +1494,7 @@
         <v>0.7432432432432432</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="D31" s="6">
         <f>D29/D27</f>
         <v>0.51948051948051943</v>
@@ -1493,7 +1504,7 @@
         <v>0.54054054054054057</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="23" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="D32" s="5">
         <v>76</v>
       </c>
@@ -1501,7 +1512,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="23" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D33" s="5">
         <v>55</v>
       </c>
@@ -1509,8 +1520,8 @@
         <v>55</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="24" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D34" s="5">
@@ -1520,7 +1531,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="23" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D35" s="6">
         <f t="shared" ref="D35:E35" si="8">D33/D32</f>
         <v>0.72368421052631582</v>
@@ -1530,7 +1541,7 @@
         <v>0.75342465753424659</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="23" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D36" s="6">
         <f t="shared" ref="D36:E36" si="9">D34/D32</f>
         <v>0.36842105263157893</v>
@@ -3139,7 +3150,7 @@
     </row>
     <row r="12" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:49" x14ac:dyDescent="0.3">
